--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2020.xlsx
@@ -15727,7 +15727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cobertura APS de vejez</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2020.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="712">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
     <t xml:space="preserve">11201</t>
@@ -349,18 +349,18 @@
     <t xml:space="preserve">Yerbas Buenas</t>
   </si>
   <si>
+    <t xml:space="preserve">13128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
     <t xml:space="preserve">6102</t>
   </si>
   <si>
     <t xml:space="preserve">Codegua</t>
   </si>
   <si>
-    <t xml:space="preserve">13128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
     <t xml:space="preserve">6117</t>
   </si>
   <si>
@@ -460,18 +460,18 @@
     <t xml:space="preserve">Hijuelas</t>
   </si>
   <si>
+    <t xml:space="preserve">5402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
     <t xml:space="preserve">6106</t>
   </si>
   <si>
     <t xml:space="preserve">Graneros</t>
   </si>
   <si>
-    <t xml:space="preserve">5402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
     <t xml:space="preserve">6109</t>
   </si>
   <si>
@@ -619,18 +619,18 @@
     <t xml:space="preserve">Buin</t>
   </si>
   <si>
+    <t xml:space="preserve">5603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartagena</t>
+  </si>
+  <si>
     <t xml:space="preserve">6301</t>
   </si>
   <si>
     <t xml:space="preserve">San Fernando</t>
   </si>
   <si>
-    <t xml:space="preserve">5603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cartagena</t>
-  </si>
-  <si>
     <t xml:space="preserve">16103</t>
   </si>
   <si>
@@ -823,18 +823,18 @@
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
+    <t xml:space="preserve">7110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
     <t xml:space="preserve">16205</t>
   </si>
   <si>
     <t xml:space="preserve">Portezuelo</t>
   </si>
   <si>
-    <t xml:space="preserve">7110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
     <t xml:space="preserve">7303</t>
   </si>
   <si>
@@ -907,18 +907,18 @@
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
+    <t xml:space="preserve">5605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Tabo</t>
+  </si>
+  <si>
     <t xml:space="preserve">13302</t>
   </si>
   <si>
     <t xml:space="preserve">Lampa</t>
   </si>
   <si>
-    <t xml:space="preserve">5605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Tabo</t>
-  </si>
-  <si>
     <t xml:space="preserve">6202</t>
   </si>
   <si>
@@ -1540,15 +1540,15 @@
     <t xml:space="preserve">Hualqui</t>
   </si>
   <si>
+    <t xml:space="preserve">14104</t>
+  </si>
+  <si>
     <t xml:space="preserve">10105</t>
   </si>
   <si>
     <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
-    <t xml:space="preserve">14104</t>
-  </si>
-  <si>
     <t xml:space="preserve">8102</t>
   </si>
   <si>
@@ -2107,7 +2107,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:28</t>
+    <t xml:space="preserve">2026-07-30 15:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2119,16 +2119,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_p_aps_a_2020.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura APS de vejez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -3997,10 +4006,10 @@
         <v>2020</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>110</v>
@@ -4029,10 +4038,10 @@
         <v>2020</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>112</v>
@@ -4573,10 +4582,10 @@
         <v>2020</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>147</v>
@@ -4605,10 +4614,10 @@
         <v>2020</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>149</v>
@@ -5437,10 +5446,10 @@
         <v>2020</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>200</v>
@@ -5469,10 +5478,10 @@
         <v>2020</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>202</v>
@@ -6525,10 +6534,10 @@
         <v>2020</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>268</v>
@@ -6557,10 +6566,10 @@
         <v>2020</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>270</v>
@@ -6973,10 +6982,10 @@
         <v>2020</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>296</v>
@@ -7005,10 +7014,10 @@
         <v>2020</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>298</v>
@@ -10173,16 +10182,16 @@
         <v>2020</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>507</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>478</v>
@@ -10205,16 +10214,16 @@
         <v>2020</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D241" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>478</v>
@@ -13229,23 +13238,23 @@
         <v>701</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -13260,28 +13269,28 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13290,7 +13299,7 @@
         <v>2020</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2020.xlsx
@@ -2107,7 +2107,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:57</t>
+    <t xml:space="preserve">2026-09-07 13:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2020.xlsx
@@ -2107,7 +2107,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:11</t>
+    <t xml:space="preserve">2026-09-08 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
